--- a/exports/trend_1d/UNOMINDA_full_report.xlsx
+++ b/exports/trend_1d/UNOMINDA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>13.73</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H2" t="n">
-        <v>18.05</v>
+        <v>17.55</v>
       </c>
       <c r="I2" t="n">
         <v>18.0120534083176</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>-12.17</v>
+        <v>-14.6</v>
       </c>
       <c r="L2" t="n">
         <v>17.03</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.4</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42207</v>
+        <v>42208</v>
       </c>
       <c r="H3" t="n">
-        <v>18.2</v>
+        <v>18.45</v>
       </c>
       <c r="I3" t="n">
         <v>18.31466688180183</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.7</v>
+        <v>-5.13</v>
       </c>
       <c r="L3" t="n">
         <v>16.81</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.49</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>18.65</v>
+        <v>16.65</v>
       </c>
       <c r="I4" t="n">
         <v>17.30622425201265</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>1.08</v>
+        <v>-9.76</v>
       </c>
       <c r="L4" t="n">
-        <v>8.67</v>
+        <v>11.38</v>
       </c>
       <c r="M4" t="n">
         <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>4.22</v>
+        <v>10.72</v>
       </c>
       <c r="O4" t="n">
         <v>1.37</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>27.96</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42307</v>
+        <v>42310</v>
       </c>
       <c r="H5" t="n">
-        <v>17.35</v>
+        <v>18.95</v>
       </c>
       <c r="I5" t="n">
         <v>18.66395005462255</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.2</v>
+        <v>-13.81</v>
       </c>
       <c r="L5" t="n">
-        <v>11.11</v>
+        <v>17.12</v>
       </c>
       <c r="M5" t="n">
         <v>5.07</v>
       </c>
       <c r="N5" t="n">
-        <v>4.48</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>-10.72</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>15.51</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42382</v>
+        <v>42383</v>
       </c>
       <c r="H6" t="n">
-        <v>27.95</v>
+        <v>27.05</v>
       </c>
       <c r="I6" t="n">
         <v>27.91626019641816</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K6" t="n">
-        <v>47.49</v>
+        <v>42.74</v>
       </c>
       <c r="L6" t="n">
         <v>10.03</v>
       </c>
       <c r="M6" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="N6" t="n">
         <v>4.92</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>18.41</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H7" t="n">
-        <v>28.1</v>
+        <v>33.05</v>
       </c>
       <c r="I7" t="n">
         <v>29.3700254768909</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.88</v>
+        <v>-22.18</v>
       </c>
       <c r="L7" t="n">
-        <v>13.86</v>
+        <v>23.84</v>
       </c>
       <c r="M7" t="n">
-        <v>5.66</v>
+        <v>6.05</v>
       </c>
       <c r="N7" t="n">
-        <v>8.199999999999999</v>
+        <v>17.62</v>
       </c>
       <c r="O7" t="n">
         <v>-3.22</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>22.19</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H8" t="n">
-        <v>56.45</v>
+        <v>52.25</v>
       </c>
       <c r="I8" t="n">
         <v>56.28235881342795</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K8" t="n">
-        <v>70.8</v>
+        <v>58.09</v>
       </c>
       <c r="L8" t="n">
         <v>11.2</v>
@@ -897,7 +992,7 @@
         <v>15.38</v>
       </c>
       <c r="N8" t="n">
-        <v>6.48</v>
+        <v>7.44</v>
       </c>
       <c r="O8" t="n">
         <v>17.62</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>28.57</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42751</v>
+        <v>42752</v>
       </c>
       <c r="H9" t="n">
-        <v>55.15</v>
+        <v>56.85</v>
       </c>
       <c r="I9" t="n">
         <v>56.34012023426481</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.55</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>8.33</v>
+        <v>10.33</v>
       </c>
       <c r="M9" t="n">
         <v>3.51</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.12</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43018</v>
+        <v>43019</v>
       </c>
       <c r="H10" t="n">
-        <v>136.4</v>
+        <v>135.4</v>
       </c>
       <c r="I10" t="n">
         <v>135.5285339868555</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K10" t="n">
-        <v>139.93</v>
+        <v>138.17</v>
       </c>
       <c r="L10" t="n">
         <v>3.25</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>11.15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43040</v>
+        <v>43041</v>
       </c>
       <c r="H11" t="n">
-        <v>147.75</v>
+        <v>150.35</v>
       </c>
       <c r="I11" t="n">
         <v>148.176883669524</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.119999999999999</v>
+        <v>-11.04</v>
       </c>
       <c r="L11" t="n">
-        <v>9.56</v>
+        <v>13.85</v>
       </c>
       <c r="M11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="N11" t="n">
         <v>8.08</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.56</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43133</v>
+        <v>43136</v>
       </c>
       <c r="H12" t="n">
-        <v>202.15</v>
+        <v>191.75</v>
       </c>
       <c r="I12" t="n">
         <v>199.372944154753</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K12" t="n">
-        <v>34.45</v>
+        <v>27.54</v>
       </c>
       <c r="L12" t="n">
         <v>2.66</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>15.52</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43242</v>
+        <v>43243</v>
       </c>
       <c r="H13" t="n">
-        <v>187.35</v>
+        <v>213.9</v>
       </c>
       <c r="I13" t="n">
         <v>191.7413247335855</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K13" t="n">
-        <v>2.29</v>
+        <v>-11.55</v>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>13.43</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>4.08</v>
       </c>
       <c r="N13" t="n">
-        <v>6.86</v>
+        <v>14.17</v>
       </c>
       <c r="O13" t="n">
         <v>-5.14</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>15.86</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H14" t="n">
-        <v>203.75</v>
+        <v>188.4</v>
       </c>
       <c r="I14" t="n">
         <v>192.7403715589974</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.75</v>
+        <v>-11.92</v>
       </c>
       <c r="L14" t="n">
-        <v>9.23</v>
+        <v>13.44</v>
       </c>
       <c r="M14" t="n">
         <v>1.22</v>
       </c>
       <c r="N14" t="n">
-        <v>2.72</v>
+        <v>7.53</v>
       </c>
       <c r="O14" t="n">
         <v>14.17</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>18.88</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43416</v>
+        <v>43417</v>
       </c>
       <c r="H15" t="n">
-        <v>174.4</v>
+        <v>176.15</v>
       </c>
       <c r="I15" t="n">
         <v>174.9967674531126</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K15" t="n">
-        <v>7.43</v>
+        <v>6.5</v>
       </c>
       <c r="L15" t="n">
         <v>21.82</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>14.41</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H16" t="n">
-        <v>161.05</v>
+        <v>157.4</v>
       </c>
       <c r="I16" t="n">
         <v>158.5089370916359</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.57</v>
+        <v>-10.64</v>
       </c>
       <c r="L16" t="n">
         <v>15.13</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>2.2</v>
       </c>
       <c r="N16" t="n">
         <v>6.52</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.42</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43515</v>
+        <v>43516</v>
       </c>
       <c r="H17" t="n">
-        <v>143.5</v>
+        <v>162.75</v>
       </c>
       <c r="I17" t="n">
         <v>150.9167533275902</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K17" t="n">
-        <v>8.83</v>
+        <v>-3.4</v>
       </c>
       <c r="L17" t="n">
         <v>7.18</v>
@@ -1410,7 +1613,7 @@
         <v>2.26</v>
       </c>
       <c r="N17" t="n">
-        <v>4.74</v>
+        <v>13.41</v>
       </c>
       <c r="O17" t="n">
         <v>-2.27</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>18.37</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43552</v>
+        <v>43553</v>
       </c>
       <c r="H18" t="n">
-        <v>167.95</v>
+        <v>163.2</v>
       </c>
       <c r="I18" t="n">
         <v>163.5383787739302</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>0.28</v>
       </c>
       <c r="L18" t="n">
         <v>11.52</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>14.7</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43570</v>
+        <v>43571</v>
       </c>
       <c r="H19" t="n">
-        <v>175.7</v>
+        <v>188.2</v>
       </c>
       <c r="I19" t="n">
         <v>186.1615257597186</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.66</v>
+        <v>-15.32</v>
       </c>
       <c r="L19" t="n">
-        <v>8.06</v>
+        <v>17.13</v>
       </c>
       <c r="M19" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="N19" t="n">
-        <v>5.51</v>
+        <v>7.11</v>
       </c>
       <c r="O19" t="n">
         <v>-2.83</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>13.9</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43598</v>
+        <v>43599</v>
       </c>
       <c r="H20" t="n">
-        <v>172.45</v>
+        <v>168.75</v>
       </c>
       <c r="I20" t="n">
         <v>170.8444146723565</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.369999999999999</v>
+        <v>-10.33</v>
       </c>
       <c r="L20" t="n">
-        <v>9.67</v>
+        <v>11.48</v>
       </c>
       <c r="M20" t="n">
         <v>2.29</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>12.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43612</v>
+        <v>43613</v>
       </c>
       <c r="H21" t="n">
-        <v>181</v>
+        <v>183.75</v>
       </c>
       <c r="I21" t="n">
         <v>182.9608719393281</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.26</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>8.15</v>
+        <v>9.93</v>
       </c>
       <c r="M21" t="n">
         <v>4.31</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>12.84</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43634</v>
+        <v>43635</v>
       </c>
       <c r="H22" t="n">
-        <v>163.4</v>
+        <v>157.05</v>
       </c>
       <c r="I22" t="n">
         <v>160.1602723676224</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.07</v>
+        <v>-14.53</v>
       </c>
       <c r="L22" t="n">
-        <v>11.84</v>
+        <v>15.32</v>
       </c>
       <c r="M22" t="n">
         <v>0.92</v>
       </c>
       <c r="N22" t="n">
-        <v>3.55</v>
+        <v>3.89</v>
       </c>
       <c r="O22" t="n">
         <v>1.52</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>12.27</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43685</v>
+        <v>43686</v>
       </c>
       <c r="H23" t="n">
-        <v>159.85</v>
+        <v>164.3</v>
       </c>
       <c r="I23" t="n">
         <v>161.6578376990918</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.78</v>
+        <v>-4.62</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>5.57</v>
       </c>
       <c r="M23" t="n">
         <v>1.78</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.11</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43780</v>
+        <v>43782</v>
       </c>
       <c r="H24" t="n">
-        <v>167.5</v>
+        <v>163.45</v>
       </c>
       <c r="I24" t="n">
         <v>165.9933731490888</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K24" t="n">
-        <v>1.95</v>
+        <v>-0.52</v>
       </c>
       <c r="L24" t="n">
         <v>9.25</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>13.35</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43838</v>
+        <v>43839</v>
       </c>
       <c r="H25" t="n">
-        <v>181</v>
+        <v>191.75</v>
       </c>
       <c r="I25" t="n">
         <v>185.0108757426048</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K25" t="n">
-        <v>-10.74</v>
+        <v>-17.31</v>
       </c>
       <c r="L25" t="n">
-        <v>14.71</v>
+        <v>20.56</v>
       </c>
       <c r="M25" t="n">
         <v>1.85</v>
       </c>
       <c r="N25" t="n">
-        <v>2.97</v>
+        <v>5.94</v>
       </c>
       <c r="O25" t="n">
         <v>-2.42</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.64</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H26" t="n">
-        <v>186.55</v>
+        <v>182.95</v>
       </c>
       <c r="I26" t="n">
         <v>185.8218136778382</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.71</v>
+        <v>-4.59</v>
       </c>
       <c r="L26" t="n">
         <v>9.75</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.05</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44019</v>
+        <v>44020</v>
       </c>
       <c r="H27" t="n">
-        <v>149</v>
+        <v>152.7</v>
       </c>
       <c r="I27" t="n">
         <v>149.9136711840991</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K27" t="n">
-        <v>18.56</v>
+        <v>16.53</v>
       </c>
       <c r="L27" t="n">
         <v>3.28</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44441</v>
+        <v>44442</v>
       </c>
       <c r="H28" t="n">
-        <v>348.5</v>
+        <v>342.2</v>
       </c>
       <c r="I28" t="n">
         <v>344.0943937775374</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K28" t="n">
-        <v>128.23</v>
+        <v>124.1</v>
       </c>
       <c r="L28" t="n">
         <v>9.949999999999999</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>290</v>
+        <v>291</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>15</v>
+      </c>
+      <c r="U28" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.53</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44475</v>
+        <v>44476</v>
       </c>
       <c r="H29" t="n">
-        <v>367</v>
+        <v>387.4</v>
       </c>
       <c r="I29" t="n">
         <v>381.6397657226775</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.25</v>
+        <v>-13.21</v>
       </c>
       <c r="L29" t="n">
-        <v>10.42</v>
+        <v>14.26</v>
       </c>
       <c r="M29" t="n">
         <v>1.36</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>5.56</v>
       </c>
       <c r="O29" t="n">
         <v>-1.81</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.96</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44585</v>
+        <v>44586</v>
       </c>
       <c r="H30" t="n">
-        <v>535.75</v>
+        <v>511.8</v>
       </c>
       <c r="I30" t="n">
         <v>519.3602856093752</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K30" t="n">
-        <v>38.29</v>
+        <v>32.11</v>
       </c>
       <c r="L30" t="n">
         <v>5.52</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>17.69</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44743</v>
+        <v>44746</v>
       </c>
       <c r="H31" t="n">
-        <v>472.15</v>
+        <v>479.4</v>
       </c>
       <c r="I31" t="n">
         <v>475.3492490513755</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K31" t="n">
-        <v>7.75</v>
+        <v>6.33</v>
       </c>
       <c r="L31" t="n">
         <v>14.52</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.8</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H32" t="n">
-        <v>543.7</v>
+        <v>531.25</v>
       </c>
       <c r="I32" t="n">
         <v>538.2146547383646</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K32" t="n">
-        <v>13.41</v>
+        <v>10.82</v>
       </c>
       <c r="L32" t="n">
         <v>1.72</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.49</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44966</v>
+        <v>44967</v>
       </c>
       <c r="H33" t="n">
-        <v>525.95</v>
+        <v>533</v>
       </c>
       <c r="I33" t="n">
         <v>527.9272132568223</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>-0.33</v>
       </c>
       <c r="L33" t="n">
         <v>8.880000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44998</v>
+        <v>44999</v>
       </c>
       <c r="H34" t="n">
-        <v>495.2</v>
+        <v>483.6</v>
       </c>
       <c r="I34" t="n">
         <v>484.2347179595812</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.09</v>
+        <v>-9.27</v>
       </c>
       <c r="L34" t="n">
-        <v>8.380000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="M34" t="n">
         <v>0.8100000000000001</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45022</v>
+        <v>45026</v>
       </c>
       <c r="H35" t="n">
-        <v>480.25</v>
+        <v>502.95</v>
       </c>
       <c r="I35" t="n">
         <v>485.940047487685</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6899999999999999</v>
+        <v>-4</v>
       </c>
       <c r="L35" t="n">
-        <v>3.06</v>
+        <v>5.05</v>
       </c>
       <c r="M35" t="n">
         <v>2.65</v>
       </c>
       <c r="N35" t="n">
-        <v>3.64</v>
+        <v>4.73</v>
       </c>
       <c r="O35" t="n">
         <v>-2.34</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.81</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H36" t="n">
-        <v>605.25</v>
+        <v>578.2</v>
       </c>
       <c r="I36" t="n">
         <v>581.3523709220644</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K36" t="n">
-        <v>20.34</v>
+        <v>14.96</v>
       </c>
       <c r="L36" t="n">
         <v>5.16</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45238</v>
+        <v>45239</v>
       </c>
       <c r="H37" t="n">
-        <v>602</v>
+        <v>631.35</v>
       </c>
       <c r="I37" t="n">
         <v>615.2032207713439</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.12</v>
+        <v>-9.19</v>
       </c>
       <c r="L37" t="n">
-        <v>5.67</v>
+        <v>10</v>
       </c>
       <c r="M37" t="n">
         <v>1.37</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>4.88</v>
       </c>
       <c r="O37" t="n">
         <v>-4.47</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.22</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45329</v>
+        <v>45330</v>
       </c>
       <c r="H38" t="n">
-        <v>682.2</v>
+        <v>653.3</v>
       </c>
       <c r="I38" t="n">
         <v>662.0967046671412</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K38" t="n">
-        <v>8.050000000000001</v>
+        <v>3.48</v>
       </c>
       <c r="L38" t="n">
         <v>4.06</v>
@@ -2607,7 +3062,7 @@
         <v>2.89</v>
       </c>
       <c r="N38" t="n">
-        <v>2.32</v>
+        <v>4.24</v>
       </c>
       <c r="O38" t="n">
         <v>4.88</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>11.5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="H39" t="n">
-        <v>673.8</v>
+        <v>686</v>
       </c>
       <c r="I39" t="n">
         <v>677.7955145609496</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.14</v>
+        <v>-5.01</v>
       </c>
       <c r="L39" t="n">
-        <v>5.54</v>
+        <v>5.62</v>
       </c>
       <c r="M39" t="n">
         <v>3.97</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.74</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H40" t="n">
-        <v>1021.15</v>
+        <v>993.75</v>
       </c>
       <c r="I40" t="n">
         <v>1018.661609163812</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K40" t="n">
-        <v>48.86</v>
+        <v>44.86</v>
       </c>
       <c r="L40" t="n">
         <v>2.52</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>17.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45517</v>
+        <v>45518</v>
       </c>
       <c r="H41" t="n">
-        <v>1047.9</v>
+        <v>1107</v>
       </c>
       <c r="I41" t="n">
         <v>1091.386179098633</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.45</v>
+        <v>-11.4</v>
       </c>
       <c r="L41" t="n">
-        <v>8.359999999999999</v>
+        <v>12.78</v>
       </c>
       <c r="M41" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>3.86</v>
+        <v>5.64</v>
       </c>
       <c r="O41" t="n">
         <v>-2.68</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>15.16</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H42" t="n">
-        <v>1036.1</v>
+        <v>1027</v>
       </c>
       <c r="I42" t="n">
         <v>1035.571258514699</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.4</v>
+        <v>-7.23</v>
       </c>
       <c r="L42" t="n">
-        <v>7.26</v>
+        <v>9.06</v>
       </c>
       <c r="M42" t="n">
         <v>1.94</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>14.54</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="H43" t="n">
-        <v>998.1</v>
+        <v>1040.3</v>
       </c>
       <c r="I43" t="n">
         <v>1035.504921670057</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K43" t="n">
-        <v>2.81</v>
+        <v>-1.3</v>
       </c>
       <c r="L43" t="n">
         <v>14.76</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>15.31</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="H44" t="n">
-        <v>976.5</v>
+        <v>967.95</v>
       </c>
       <c r="I44" t="n">
         <v>972.4620318078271</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.13</v>
+        <v>-6.95</v>
       </c>
       <c r="L44" t="n">
-        <v>7.11</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>1.61</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>14.33</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45692</v>
+        <v>45693</v>
       </c>
       <c r="H45" t="n">
-        <v>1001.5</v>
+        <v>1024.3</v>
       </c>
       <c r="I45" t="n">
         <v>1021.572830433041</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.47</v>
+        <v>-5.82</v>
       </c>
       <c r="L45" t="n">
-        <v>3.71</v>
+        <v>6.18</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>14.01</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H46" t="n">
-        <v>946.85</v>
+        <v>906.25</v>
       </c>
       <c r="I46" t="n">
         <v>926.5195324008657</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.56</v>
+        <v>-11.52</v>
       </c>
       <c r="L46" t="n">
-        <v>8.92</v>
+        <v>12.49</v>
       </c>
       <c r="M46" t="n">
         <v>1.67</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>18.51</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H47" t="n">
-        <v>935.5</v>
+        <v>981.5</v>
       </c>
       <c r="I47" t="n">
         <v>941.4092611488279</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.23</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>4.72</v>
+        <v>8.91</v>
       </c>
       <c r="M47" t="n">
         <v>1.03</v>
       </c>
       <c r="N47" t="n">
-        <v>4.9</v>
+        <v>4.92</v>
       </c>
       <c r="O47" t="n">
         <v>-4.29</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>14.7</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45749</v>
+        <v>45750</v>
       </c>
       <c r="H48" t="n">
-        <v>881.8</v>
+        <v>863.7</v>
       </c>
       <c r="I48" t="n">
         <v>874.98794538099</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.16</v>
+        <v>-12</v>
       </c>
       <c r="L48" t="n">
         <v>13.13</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>14.63</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45783</v>
+        <v>45784</v>
       </c>
       <c r="H49" t="n">
-        <v>908.85</v>
+        <v>927.5</v>
       </c>
       <c r="I49" t="n">
         <v>920.6890949794856</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.23</v>
+        <v>-7.39</v>
       </c>
       <c r="L49" t="n">
         <v>8.800000000000001</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>13.94</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="H50" t="n">
-        <v>1069.8</v>
+        <v>1041.4</v>
       </c>
       <c r="I50" t="n">
         <v>1046.215902771541</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K50" t="n">
-        <v>15.34</v>
+        <v>12.28</v>
       </c>
       <c r="L50" t="n">
         <v>4.57</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>8.4</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45882</v>
+        <v>45883</v>
       </c>
       <c r="H51" t="n">
-        <v>1114.4</v>
+        <v>1149.8</v>
       </c>
       <c r="I51" t="n">
         <v>1127.260661345488</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.01</v>
+        <v>-10.41</v>
       </c>
       <c r="L51" t="n">
-        <v>7.87</v>
+        <v>10.81</v>
       </c>
       <c r="M51" t="n">
         <v>0.44</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.45</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H52" t="n">
-        <v>1260</v>
+        <v>1219.8</v>
       </c>
       <c r="I52" t="n">
         <v>1240.900802992401</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K52" t="n">
-        <v>9.58</v>
+        <v>6.09</v>
       </c>
       <c r="L52" t="n">
         <v>3.08</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>12.23</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="H53" t="n">
-        <v>1229.7</v>
+        <v>1319.3</v>
       </c>
       <c r="I53" t="n">
         <v>1294.018720962582</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-8.16</v>
       </c>
       <c r="L53" t="n">
-        <v>4.6</v>
+        <v>8.85</v>
       </c>
       <c r="M53" t="n">
         <v>0.79</v>
       </c>
       <c r="N53" t="n">
-        <v>2.38</v>
+        <v>7.29</v>
       </c>
       <c r="O53" t="n">
         <v>-3.19</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>12.84</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="H54" t="n">
-        <v>1249.8</v>
+        <v>1210</v>
       </c>
       <c r="I54" t="n">
         <v>1245.135141223016</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.27</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>7.9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M54" t="n">
         <v>0.9399999999999999</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="H55" t="n">
-        <v>1204.8</v>
+        <v>1230.8</v>
       </c>
       <c r="I55" t="n">
         <v>1226.734889758366</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>0.43</v>
+        <v>-1.72</v>
       </c>
       <c r="L55" t="n">
         <v>3.22</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>12.5</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H56" t="n">
-        <v>1121.3</v>
+        <v>1082.1</v>
       </c>
       <c r="I56" t="n">
         <v>1107.164303747943</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>-8.9</v>
+        <v>-12.08</v>
       </c>
       <c r="L56" t="n">
-        <v>10.85</v>
+        <v>15.66</v>
       </c>
       <c r="M56" t="n">
         <v>4.92</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>10.86</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H57" t="n">
-        <v>1129.4</v>
+        <v>1149.6</v>
       </c>
       <c r="I57" t="n">
         <v>1143.374999961234</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.37</v>
+        <v>-6.24</v>
       </c>
       <c r="L57" t="n">
-        <v>4.98</v>
+        <v>6.85</v>
       </c>
       <c r="M57" t="n">
         <v>3.78</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>11.71</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="H58" t="n">
-        <v>1067.8</v>
+        <v>1051.9</v>
       </c>
       <c r="I58" t="n">
         <v>1053.623432404142</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K58" t="n">
-        <v>-7.12</v>
+        <v>-8.5</v>
       </c>
       <c r="L58" t="n">
-        <v>7.79</v>
+        <v>12.36</v>
       </c>
       <c r="M58" t="n">
         <v>1.19</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>10.98</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H59" t="n">
-        <v>1163.9</v>
+        <v>1168.7</v>
       </c>
       <c r="I59" t="n">
         <v>1167.40568005971</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.65</v>
+        <v>-11.1</v>
       </c>
       <c r="L59" t="n">
-        <v>12.17</v>
+        <v>12.63</v>
       </c>
       <c r="M59" t="n">
         <v>1.98</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.76</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H60" t="n">
-        <v>1201.6</v>
+        <v>1159.7</v>
       </c>
       <c r="I60" t="n">
         <v>1200.508841211667</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K60" t="n">
-        <v>2.82</v>
+        <v>-0.77</v>
       </c>
       <c r="L60" t="n">
         <v>1.04</v>
@@ -3861,7 +4580,7 @@
         <v>0.87</v>
       </c>
       <c r="N60" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="O60" t="n">
         <v>0.41</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>10.01</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H61" t="n">
-        <v>1205</v>
+        <v>1284</v>
       </c>
       <c r="I61" t="n">
         <v>1262.767130677977</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.91</v>
+        <v>-10.72</v>
       </c>
       <c r="L61" t="n">
-        <v>5.03</v>
+        <v>10.72</v>
       </c>
       <c r="M61" t="n">
         <v>0.89</v>
       </c>
       <c r="N61" t="n">
-        <v>2.27</v>
+        <v>6.56</v>
       </c>
       <c r="O61" t="n">
         <v>-3.49</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>11.28</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H62" t="n">
-        <v>1170</v>
+        <v>1111</v>
       </c>
       <c r="I62" t="n">
         <v>1139.147124150839</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>-8.880000000000001</v>
+        <v>-13.47</v>
       </c>
       <c r="L62" t="n">
-        <v>10.48</v>
+        <v>14.4</v>
       </c>
       <c r="M62" t="n">
         <v>1.88</v>
       </c>
       <c r="N62" t="n">
-        <v>4.4</v>
+        <v>5.04</v>
       </c>
       <c r="O62" t="n">
         <v>6.56</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>18</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8993,7 +9756,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -9003,7 +9766,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -9013,7 +9776,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8">
@@ -9023,7 +9786,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9033,7 +9796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -9043,7 +9806,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -9053,7 +9816,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -9063,7 +9826,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -9073,7 +9836,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.1</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="14">
@@ -9083,7 +9846,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.65</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="15">
@@ -9093,7 +9856,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.12</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="16">
@@ -9103,7 +9866,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.09</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="17">
@@ -9113,7 +9876,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>139.93</v>
+        <v>138.17</v>
       </c>
     </row>
     <row r="18">
@@ -9123,7 +9886,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="19">
@@ -9133,7 +9896,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.35</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="20">
@@ -9143,7 +9906,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -9153,7 +9916,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.82</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="22">
@@ -9163,7 +9926,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -9173,7 +9936,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -9183,7 +9946,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -9203,7 +9966,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.29</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="27">
@@ -9213,7 +9976,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.67</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="28">
@@ -9223,7 +9986,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
